--- a/public/sample/rider_invoice_sample.xlsx
+++ b/public/sample/rider_invoice_sample.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jutt computer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62DCD1C9-367A-4ABA-A930-5873582971FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="7440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$AD$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$N$1:$AF$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -108,12 +107,6 @@
     <t>Deira</t>
   </si>
   <si>
-    <t>Liaqat Ali Bilawal Khan</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
     <t>Off</t>
   </si>
   <si>
@@ -129,28 +122,49 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Invoice Description comes here</t>
-  </si>
-  <si>
-    <t>Jan-2024</t>
-  </si>
-  <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Salman Pasha Mushtaq Ahmed</t>
+  </si>
+  <si>
+    <t>Aug-2025</t>
+  </si>
+  <si>
+    <t>Rider Orders Invoice Month of Aug-2025</t>
+  </si>
+  <si>
+    <t>If you have any discrepancies regarding this invoice, you may contact our Accounts Department within 4 days. After this period, no changes will be accepted.</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -174,11 +188,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,21 +507,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE329"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AF328"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.42578125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="17" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -584,66 +600,69 @@
         <v>24</v>
       </c>
       <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>45901</v>
+      </c>
+      <c r="B2">
+        <v>106825</v>
+      </c>
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="D2">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>45341</v>
-      </c>
-      <c r="B2">
-        <v>20163</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2">
-        <v>367</v>
-      </c>
       <c r="E2">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -667,1015 +686,1394 @@
         <v>1</v>
       </c>
       <c r="W2">
-        <v>310</v>
+        <v>86.9</v>
       </c>
       <c r="X2" t="s">
         <v>25</v>
       </c>
       <c r="Y2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AC2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AE2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="AC3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AC3" s="2"/>
+      <c r="AE3" s="4"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="AC4" s="1"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AC4" s="2"/>
+      <c r="AE4" s="4"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="AC16" s="1"/>
-    </row>
-    <row r="17" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC17" s="1"/>
-    </row>
-    <row r="18" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC18" s="1"/>
-    </row>
-    <row r="19" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC20" s="1"/>
-    </row>
-    <row r="21" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC21" s="1"/>
-    </row>
-    <row r="22" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC22" s="1"/>
-    </row>
-    <row r="23" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC23" s="1"/>
-    </row>
-    <row r="24" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC24" s="1"/>
-    </row>
-    <row r="25" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC25" s="1"/>
-    </row>
-    <row r="26" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC26" s="1"/>
-    </row>
-    <row r="27" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC27" s="1"/>
-    </row>
-    <row r="28" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC28" s="1"/>
-    </row>
-    <row r="29" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC29" s="1"/>
-    </row>
-    <row r="30" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC30" s="1"/>
-    </row>
-    <row r="31" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC31" s="1"/>
-    </row>
-    <row r="32" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC33" s="1"/>
-    </row>
-    <row r="34" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC34" s="1"/>
-    </row>
-    <row r="35" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC35" s="1"/>
-    </row>
-    <row r="36" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC36" s="1"/>
-    </row>
-    <row r="37" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC37" s="1"/>
-    </row>
-    <row r="38" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC38" s="1"/>
-    </row>
-    <row r="39" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC39" s="1"/>
-    </row>
-    <row r="40" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC40" s="1"/>
-    </row>
-    <row r="41" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC41" s="1"/>
-    </row>
-    <row r="42" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC42" s="1"/>
-    </row>
-    <row r="43" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC43" s="1"/>
-    </row>
-    <row r="44" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC44" s="1"/>
-    </row>
-    <row r="45" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC45" s="1"/>
-    </row>
-    <row r="46" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC46" s="1"/>
-    </row>
-    <row r="47" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC47" s="1"/>
-    </row>
-    <row r="48" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC48" s="1"/>
-    </row>
-    <row r="49" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC49" s="1"/>
-    </row>
-    <row r="50" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC50" s="1"/>
-    </row>
-    <row r="51" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC51" s="1"/>
-    </row>
-    <row r="52" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC52" s="1"/>
-    </row>
-    <row r="53" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC53" s="1"/>
-    </row>
-    <row r="54" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC54" s="1"/>
-    </row>
-    <row r="55" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC55" s="1"/>
-    </row>
-    <row r="56" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC56" s="1"/>
-    </row>
-    <row r="57" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC57" s="1"/>
-    </row>
-    <row r="58" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC58" s="1"/>
-    </row>
-    <row r="59" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC59" s="1"/>
-    </row>
-    <row r="60" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC60" s="1"/>
-    </row>
-    <row r="61" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC61" s="1"/>
-    </row>
-    <row r="62" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC62" s="1"/>
-    </row>
-    <row r="63" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC63" s="1"/>
-    </row>
-    <row r="64" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC64" s="1"/>
-    </row>
-    <row r="65" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC65" s="1"/>
-    </row>
-    <row r="66" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC66" s="1"/>
-    </row>
-    <row r="67" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC67" s="1"/>
-    </row>
-    <row r="68" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC68" s="1"/>
-    </row>
-    <row r="69" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC69" s="1"/>
-    </row>
-    <row r="70" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC70" s="1"/>
-    </row>
-    <row r="71" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC71" s="1"/>
-    </row>
-    <row r="72" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC72" s="1"/>
-    </row>
-    <row r="73" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC73" s="1"/>
-    </row>
-    <row r="74" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC74" s="1"/>
-    </row>
-    <row r="75" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC75" s="1"/>
-    </row>
-    <row r="76" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC76" s="1"/>
-    </row>
-    <row r="77" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC77" s="1"/>
-    </row>
-    <row r="78" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC78" s="1"/>
-    </row>
-    <row r="79" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC79" s="1"/>
-    </row>
-    <row r="80" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC80" s="1"/>
-    </row>
-    <row r="81" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC81" s="1"/>
-    </row>
-    <row r="82" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC82" s="1"/>
-    </row>
-    <row r="83" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC83" s="1"/>
-    </row>
-    <row r="84" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC84" s="1"/>
-    </row>
-    <row r="85" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC85" s="1"/>
-    </row>
-    <row r="86" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC86" s="1"/>
-    </row>
-    <row r="87" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC87" s="1"/>
-    </row>
-    <row r="88" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC88" s="1"/>
-    </row>
-    <row r="89" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC89" s="1"/>
-    </row>
-    <row r="90" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC90" s="1"/>
-    </row>
-    <row r="91" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC91" s="1"/>
-    </row>
-    <row r="92" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC92" s="1"/>
-    </row>
-    <row r="93" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC93" s="1"/>
-    </row>
-    <row r="94" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC94" s="1"/>
-    </row>
-    <row r="95" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC95" s="1"/>
-    </row>
-    <row r="96" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC96" s="1"/>
-    </row>
-    <row r="97" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC97" s="1"/>
-    </row>
-    <row r="98" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC98" s="1"/>
-    </row>
-    <row r="99" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC99" s="1"/>
-    </row>
-    <row r="100" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC100" s="1"/>
-    </row>
-    <row r="101" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC101" s="1"/>
-    </row>
-    <row r="102" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC102" s="1"/>
-    </row>
-    <row r="103" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC103" s="1"/>
-    </row>
-    <row r="104" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC104" s="1"/>
-    </row>
-    <row r="105" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC105" s="1"/>
-    </row>
-    <row r="106" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC106" s="1"/>
-    </row>
-    <row r="107" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC107" s="1"/>
-    </row>
-    <row r="108" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC108" s="1"/>
-    </row>
-    <row r="109" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC109" s="1"/>
-    </row>
-    <row r="110" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC110" s="1"/>
-    </row>
-    <row r="111" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC111" s="1"/>
-    </row>
-    <row r="112" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC112" s="1"/>
-    </row>
-    <row r="113" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC113" s="1"/>
-    </row>
-    <row r="114" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC114" s="1"/>
-    </row>
-    <row r="115" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC115" s="1"/>
-    </row>
-    <row r="116" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC116" s="1"/>
-    </row>
-    <row r="117" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC117" s="1"/>
-    </row>
-    <row r="118" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC118" s="1"/>
-    </row>
-    <row r="119" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC119" s="1"/>
-    </row>
-    <row r="120" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC120" s="1"/>
-    </row>
-    <row r="121" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC121" s="1"/>
-    </row>
-    <row r="122" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC122" s="1"/>
-    </row>
-    <row r="123" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC123" s="1"/>
-    </row>
-    <row r="124" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC124" s="1"/>
-    </row>
-    <row r="125" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC125" s="1"/>
-    </row>
-    <row r="126" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC126" s="1"/>
-    </row>
-    <row r="127" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC127" s="1"/>
-    </row>
-    <row r="128" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC128" s="1"/>
-    </row>
-    <row r="129" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC129" s="1"/>
-    </row>
-    <row r="130" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC130" s="1"/>
-    </row>
-    <row r="131" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC131" s="1"/>
-    </row>
-    <row r="132" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC132" s="1"/>
-    </row>
-    <row r="133" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC133" s="1"/>
-    </row>
-    <row r="134" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC134" s="1"/>
-    </row>
-    <row r="135" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC135" s="1"/>
-    </row>
-    <row r="136" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC136" s="1"/>
-    </row>
-    <row r="137" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC137" s="1"/>
-    </row>
-    <row r="138" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC138" s="1"/>
-    </row>
-    <row r="139" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC139" s="1"/>
-    </row>
-    <row r="140" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC140" s="1"/>
-    </row>
-    <row r="141" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC141" s="1"/>
-    </row>
-    <row r="142" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC142" s="1"/>
-    </row>
-    <row r="143" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC143" s="1"/>
-    </row>
-    <row r="144" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC144" s="1"/>
-    </row>
-    <row r="145" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC145" s="1"/>
-    </row>
-    <row r="146" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC146" s="1"/>
-    </row>
-    <row r="147" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC147" s="1"/>
-    </row>
-    <row r="148" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC148" s="1"/>
-    </row>
-    <row r="149" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC149" s="1"/>
-    </row>
-    <row r="150" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC150" s="1"/>
-    </row>
-    <row r="151" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC151" s="1"/>
-    </row>
-    <row r="152" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC152" s="1"/>
-    </row>
-    <row r="153" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC153" s="1"/>
-    </row>
-    <row r="154" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC154" s="1"/>
-    </row>
-    <row r="155" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC155" s="1"/>
-    </row>
-    <row r="156" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC156" s="1"/>
-    </row>
-    <row r="157" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC157" s="1"/>
-    </row>
-    <row r="158" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC158" s="1"/>
-    </row>
-    <row r="159" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC159" s="1"/>
-    </row>
-    <row r="160" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC160" s="1"/>
-    </row>
-    <row r="161" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC161" s="1"/>
-    </row>
-    <row r="162" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC162" s="1"/>
-    </row>
-    <row r="163" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC163" s="1"/>
-    </row>
-    <row r="164" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC164" s="1"/>
-    </row>
-    <row r="165" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC165" s="1"/>
-    </row>
-    <row r="166" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC166" s="1"/>
-    </row>
-    <row r="167" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC167" s="1"/>
-    </row>
-    <row r="168" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC168" s="1"/>
-    </row>
-    <row r="169" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC169" s="1"/>
-    </row>
-    <row r="170" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC170" s="1"/>
-    </row>
-    <row r="171" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC171" s="1"/>
-    </row>
-    <row r="172" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC172" s="1"/>
-    </row>
-    <row r="173" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC173" s="1"/>
-    </row>
-    <row r="174" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC174" s="1"/>
-    </row>
-    <row r="175" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC175" s="1"/>
-    </row>
-    <row r="176" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC176" s="1"/>
-    </row>
-    <row r="177" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC177" s="1"/>
-    </row>
-    <row r="178" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC178" s="1"/>
-    </row>
-    <row r="179" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC179" s="1"/>
-    </row>
-    <row r="180" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC180" s="1"/>
-    </row>
-    <row r="181" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC181" s="1"/>
-    </row>
-    <row r="182" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC182" s="1"/>
-    </row>
-    <row r="183" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC183" s="1"/>
-    </row>
-    <row r="184" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC184" s="1"/>
-    </row>
-    <row r="185" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC185" s="1"/>
-    </row>
-    <row r="186" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC186" s="1"/>
-    </row>
-    <row r="187" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC187" s="1"/>
-    </row>
-    <row r="188" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC188" s="1"/>
-    </row>
-    <row r="189" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC189" s="1"/>
-    </row>
-    <row r="190" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC5" s="2"/>
+      <c r="AE5" s="4"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="AC6" s="2"/>
+      <c r="AE6" s="4"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="AC7" s="2"/>
+      <c r="AE7" s="4"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="AC8" s="2"/>
+      <c r="AE8" s="4"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="AC9" s="2"/>
+      <c r="AE9" s="4"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="AC10" s="2"/>
+      <c r="AE10" s="4"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="AC11" s="2"/>
+      <c r="AE11" s="4"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="AC12" s="2"/>
+      <c r="AE12" s="4"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="AC13" s="2"/>
+      <c r="AE13" s="4"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="AC14" s="2"/>
+      <c r="AE14" s="4"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="AC15" s="2"/>
+      <c r="AE15" s="4"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="AC16" s="2"/>
+      <c r="AE16" s="4"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="AC17" s="2"/>
+      <c r="AE17" s="4"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="AC18" s="2"/>
+      <c r="AE18" s="4"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="AC19" s="2"/>
+      <c r="AE19" s="4"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="AC20" s="2"/>
+      <c r="AE20" s="4"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="AC21" s="2"/>
+      <c r="AE21" s="4"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="AC22" s="2"/>
+      <c r="AE22" s="4"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="AC23" s="2"/>
+      <c r="AE23" s="4"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="AC24" s="2"/>
+      <c r="AE24" s="4"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="AC25" s="2"/>
+      <c r="AE25" s="4"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="AC26" s="2"/>
+      <c r="AE26" s="4"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="AC27" s="2"/>
+      <c r="AE27" s="4"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="AC28" s="2"/>
+      <c r="AE28" s="4"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="AC29" s="2"/>
+      <c r="AE29" s="4"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="AC30" s="2"/>
+      <c r="AE30" s="4"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="AC31" s="2"/>
+      <c r="AE31" s="4"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="AC32" s="2"/>
+      <c r="AE32" s="4"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="AC33" s="2"/>
+      <c r="AE33" s="4"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="AC34" s="2"/>
+      <c r="AE34" s="4"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="AC35" s="2"/>
+      <c r="AE35" s="4"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="AC36" s="2"/>
+      <c r="AE36" s="4"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="AC37" s="2"/>
+      <c r="AE37" s="4"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="AC38" s="2"/>
+      <c r="AE38" s="4"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="AC39" s="2"/>
+      <c r="AE39" s="4"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="AC40" s="2"/>
+      <c r="AE40" s="4"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="AC41" s="2"/>
+      <c r="AE41" s="4"/>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="AC42" s="2"/>
+      <c r="AE42" s="4"/>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="AC43" s="2"/>
+      <c r="AE43" s="4"/>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="AC44" s="2"/>
+      <c r="AE44" s="4"/>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="AC45" s="2"/>
+      <c r="AE45" s="4"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="AC46" s="2"/>
+      <c r="AE46" s="4"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="AC47" s="2"/>
+      <c r="AE47" s="4"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="AC48" s="2"/>
+      <c r="AE48" s="4"/>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="AC49" s="2"/>
+      <c r="AE49" s="4"/>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="AC50" s="2"/>
+      <c r="AE50" s="4"/>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="AC51" s="2"/>
+      <c r="AE51" s="4"/>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="AC52" s="2"/>
+      <c r="AE52" s="4"/>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="AC53" s="2"/>
+      <c r="AE53" s="4"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="AC54" s="2"/>
+      <c r="AE54" s="4"/>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="AC55" s="2"/>
+      <c r="AE55" s="4"/>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="AC56" s="2"/>
+      <c r="AE56" s="4"/>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="AC57" s="2"/>
+      <c r="AE57" s="4"/>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="AC58" s="2"/>
+      <c r="AE58" s="4"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="AC59" s="2"/>
+      <c r="AE59" s="4"/>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="AC60" s="2"/>
+      <c r="AE60" s="4"/>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="AC61" s="2"/>
+      <c r="AE61" s="4"/>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="AC62" s="2"/>
+      <c r="AE62" s="4"/>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="AC63" s="2"/>
+      <c r="AE63" s="4"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="AC64" s="2"/>
+      <c r="AE64" s="4"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="AC65" s="2"/>
+      <c r="AE65" s="4"/>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="AC66" s="2"/>
+      <c r="AE66" s="4"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="AC67" s="2"/>
+      <c r="AE67" s="4"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="AC68" s="2"/>
+      <c r="AE68" s="4"/>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="AC69" s="2"/>
+      <c r="AE69" s="4"/>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="AC70" s="2"/>
+      <c r="AE70" s="4"/>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="AC71" s="2"/>
+      <c r="AE71" s="4"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="AC72" s="2"/>
+      <c r="AE72" s="4"/>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="AC73" s="2"/>
+      <c r="AE73" s="4"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="AC74" s="2"/>
+      <c r="AE74" s="4"/>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="AC75" s="2"/>
+      <c r="AE75" s="4"/>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="AC76" s="2"/>
+      <c r="AE76" s="4"/>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="AC77" s="2"/>
+      <c r="AE77" s="4"/>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="AC78" s="2"/>
+      <c r="AE78" s="4"/>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="AC79" s="2"/>
+      <c r="AE79" s="4"/>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="AC80" s="2"/>
+      <c r="AE80" s="4"/>
+    </row>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="AC81" s="2"/>
+      <c r="AE81" s="4"/>
+    </row>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="AC82" s="2"/>
+      <c r="AE82" s="4"/>
+    </row>
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="AC83" s="2"/>
+      <c r="AE83" s="4"/>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="AC84" s="2"/>
+      <c r="AE84" s="4"/>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+      <c r="AC85" s="2"/>
+      <c r="AE85" s="4"/>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+      <c r="AC86" s="2"/>
+      <c r="AE86" s="4"/>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+      <c r="AC87" s="2"/>
+      <c r="AE87" s="4"/>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+      <c r="AC88" s="2"/>
+      <c r="AE88" s="4"/>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="AC89" s="2"/>
+      <c r="AE89" s="4"/>
+    </row>
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+      <c r="AC90" s="2"/>
+      <c r="AE90" s="4"/>
+    </row>
+    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="AC91" s="2"/>
+      <c r="AE91" s="4"/>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+      <c r="AC92" s="2"/>
+      <c r="AE92" s="4"/>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+      <c r="AC93" s="2"/>
+      <c r="AE93" s="4"/>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+      <c r="AC94" s="2"/>
+      <c r="AE94" s="4"/>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+      <c r="AC95" s="2"/>
+      <c r="AE95" s="4"/>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
+      <c r="AC96" s="2"/>
+      <c r="AE96" s="4"/>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+      <c r="AC97" s="2"/>
+      <c r="AE97" s="4"/>
+    </row>
+    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+      <c r="AC98" s="2"/>
+      <c r="AE98" s="4"/>
+    </row>
+    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="AC99" s="2"/>
+      <c r="AE99" s="4"/>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
+      <c r="AC100" s="2"/>
+      <c r="AE100" s="4"/>
+    </row>
+    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+      <c r="AC101" s="2"/>
+      <c r="AE101" s="4"/>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+      <c r="AC102" s="2"/>
+      <c r="AE102" s="4"/>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="AC103" s="2"/>
+      <c r="AE103" s="4"/>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A104" s="3"/>
+      <c r="AC104" s="2"/>
+      <c r="AE104" s="4"/>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A105" s="3"/>
+      <c r="AC105" s="2"/>
+      <c r="AE105" s="4"/>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
+      <c r="AC106" s="2"/>
+      <c r="AE106" s="4"/>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+      <c r="AC107" s="2"/>
+      <c r="AE107" s="4"/>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+      <c r="AC108" s="2"/>
+      <c r="AE108" s="4"/>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="AC109" s="2"/>
+      <c r="AE109" s="4"/>
+    </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+      <c r="AC110" s="2"/>
+      <c r="AE110" s="4"/>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+      <c r="AC111" s="2"/>
+      <c r="AE111" s="4"/>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A112" s="3"/>
+      <c r="AC112" s="2"/>
+      <c r="AE112" s="4"/>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="AC113" s="2"/>
+      <c r="AE113" s="4"/>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="AC114" s="2"/>
+      <c r="AE114" s="4"/>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="AC115" s="2"/>
+      <c r="AE115" s="4"/>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="AC116" s="2"/>
+      <c r="AE116" s="4"/>
+    </row>
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="AC117" s="2"/>
+      <c r="AE117" s="4"/>
+    </row>
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="AC118" s="2"/>
+      <c r="AE118" s="4"/>
+    </row>
+    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="AC119" s="2"/>
+      <c r="AE119" s="4"/>
+    </row>
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+      <c r="AC120" s="2"/>
+      <c r="AE120" s="4"/>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A121" s="3"/>
+      <c r="AC121" s="2"/>
+      <c r="AE121" s="4"/>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+      <c r="AC122" s="2"/>
+      <c r="AE122" s="4"/>
+    </row>
+    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A123" s="3"/>
+      <c r="AC123" s="2"/>
+      <c r="AE123" s="4"/>
+    </row>
+    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A124" s="3"/>
+      <c r="AC124" s="2"/>
+      <c r="AE124" s="4"/>
+    </row>
+    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A125" s="3"/>
+      <c r="AC125" s="2"/>
+      <c r="AE125" s="4"/>
+    </row>
+    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A126" s="3"/>
+      <c r="AC126" s="2"/>
+      <c r="AE126" s="4"/>
+    </row>
+    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A127" s="3"/>
+      <c r="AC127" s="2"/>
+      <c r="AE127" s="4"/>
+    </row>
+    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A128" s="3"/>
+      <c r="AC128" s="2"/>
+      <c r="AE128" s="4"/>
+    </row>
+    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A129" s="3"/>
+      <c r="AC129" s="2"/>
+      <c r="AE129" s="4"/>
+    </row>
+    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+      <c r="AC130" s="2"/>
+      <c r="AE130" s="4"/>
+    </row>
+    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="AC131" s="2"/>
+      <c r="AE131" s="4"/>
+    </row>
+    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+      <c r="AC132" s="2"/>
+      <c r="AE132" s="4"/>
+    </row>
+    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A133" s="3"/>
+      <c r="AC133" s="2"/>
+      <c r="AE133" s="4"/>
+    </row>
+    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A134" s="3"/>
+      <c r="AC134" s="2"/>
+      <c r="AE134" s="4"/>
+    </row>
+    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A135" s="3"/>
+      <c r="AC135" s="2"/>
+      <c r="AE135" s="4"/>
+    </row>
+    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A136" s="3"/>
+      <c r="AC136" s="2"/>
+      <c r="AE136" s="4"/>
+    </row>
+    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A137" s="3"/>
+      <c r="AC137" s="2"/>
+      <c r="AE137" s="4"/>
+    </row>
+    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A138" s="3"/>
+      <c r="AC138" s="2"/>
+      <c r="AE138" s="4"/>
+    </row>
+    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A139" s="3"/>
+      <c r="AC139" s="2"/>
+      <c r="AE139" s="4"/>
+    </row>
+    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A140" s="3"/>
+      <c r="AC140" s="2"/>
+      <c r="AE140" s="4"/>
+    </row>
+    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A141" s="3"/>
+      <c r="AC141" s="2"/>
+      <c r="AE141" s="4"/>
+    </row>
+    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="AC142" s="2"/>
+      <c r="AE142" s="4"/>
+    </row>
+    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A143" s="3"/>
+      <c r="AC143" s="2"/>
+      <c r="AE143" s="4"/>
+    </row>
+    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A144" s="3"/>
+      <c r="AC144" s="2"/>
+      <c r="AE144" s="4"/>
+    </row>
+    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A145" s="3"/>
+      <c r="AC145" s="2"/>
+      <c r="AE145" s="4"/>
+    </row>
+    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A146" s="3"/>
+      <c r="AC146" s="2"/>
+      <c r="AE146" s="4"/>
+    </row>
+    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A147" s="3"/>
+      <c r="AC147" s="2"/>
+      <c r="AE147" s="4"/>
+    </row>
+    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A148" s="3"/>
+      <c r="AC148" s="2"/>
+      <c r="AE148" s="4"/>
+    </row>
+    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A149" s="3"/>
+      <c r="AC149" s="2"/>
+      <c r="AE149" s="4"/>
+    </row>
+    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A150" s="3"/>
+      <c r="AC150" s="2"/>
+      <c r="AE150" s="4"/>
+    </row>
+    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A151" s="3"/>
+      <c r="AC151" s="2"/>
+      <c r="AE151" s="4"/>
+    </row>
+    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A152" s="3"/>
+      <c r="AC152" s="2"/>
+      <c r="AE152" s="4"/>
+    </row>
+    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+      <c r="AC153" s="2"/>
+      <c r="AE153" s="4"/>
+    </row>
+    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A154" s="3"/>
+      <c r="AC154" s="2"/>
+      <c r="AE154" s="4"/>
+    </row>
+    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A155" s="3"/>
+      <c r="AC155" s="2"/>
+      <c r="AE155" s="4"/>
+    </row>
+    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A156" s="3"/>
+      <c r="AC156" s="2"/>
+      <c r="AE156" s="4"/>
+    </row>
+    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A157" s="3"/>
+      <c r="AC157" s="2"/>
+      <c r="AE157" s="4"/>
+    </row>
+    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A158" s="3"/>
+      <c r="AC158" s="2"/>
+      <c r="AE158" s="4"/>
+    </row>
+    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A159" s="3"/>
+      <c r="AC159" s="2"/>
+      <c r="AE159" s="4"/>
+    </row>
+    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A160" s="3"/>
+      <c r="AC160" s="2"/>
+      <c r="AE160" s="4"/>
+    </row>
+    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A161" s="3"/>
+      <c r="AC161" s="2"/>
+      <c r="AE161" s="4"/>
+    </row>
+    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A162" s="3"/>
+      <c r="AC162" s="2"/>
+      <c r="AE162" s="4"/>
+    </row>
+    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A163" s="3"/>
+      <c r="AC163" s="2"/>
+      <c r="AE163" s="4"/>
+    </row>
+    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A164" s="3"/>
+      <c r="AC164" s="2"/>
+      <c r="AE164" s="4"/>
+    </row>
+    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A165" s="3"/>
+      <c r="AC165" s="2"/>
+      <c r="AE165" s="4"/>
+    </row>
+    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A166" s="3"/>
+      <c r="AC166" s="2"/>
+      <c r="AE166" s="4"/>
+    </row>
+    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A167" s="3"/>
+      <c r="AC167" s="2"/>
+      <c r="AE167" s="4"/>
+    </row>
+    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A168" s="3"/>
+      <c r="AC168" s="2"/>
+      <c r="AE168" s="4"/>
+    </row>
+    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A169" s="3"/>
+      <c r="AC169" s="2"/>
+      <c r="AE169" s="4"/>
+    </row>
+    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A170" s="3"/>
+      <c r="AC170" s="2"/>
+      <c r="AE170" s="4"/>
+    </row>
+    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A171" s="3"/>
+      <c r="AC171" s="2"/>
+      <c r="AE171" s="4"/>
+    </row>
+    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A172" s="3"/>
+      <c r="AC172" s="2"/>
+      <c r="AE172" s="4"/>
+    </row>
+    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A173" s="3"/>
+      <c r="AC173" s="2"/>
+      <c r="AE173" s="4"/>
+    </row>
+    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A174" s="3"/>
+      <c r="AC174" s="2"/>
+      <c r="AE174" s="4"/>
+    </row>
+    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A175" s="3"/>
+      <c r="AC175" s="2"/>
+      <c r="AE175" s="4"/>
+    </row>
+    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A176" s="3"/>
+      <c r="AC176" s="2"/>
+      <c r="AE176" s="4"/>
+    </row>
+    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A177" s="3"/>
+      <c r="AC177" s="2"/>
+      <c r="AE177" s="4"/>
+    </row>
+    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A178" s="3"/>
+      <c r="AC178" s="2"/>
+      <c r="AE178" s="4"/>
+    </row>
+    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A179" s="3"/>
+      <c r="AC179" s="2"/>
+      <c r="AE179" s="4"/>
+    </row>
+    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A180" s="3"/>
+      <c r="AC180" s="2"/>
+      <c r="AE180" s="4"/>
+    </row>
+    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A181" s="3"/>
+      <c r="AC181" s="2"/>
+      <c r="AE181" s="4"/>
+    </row>
+    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A182" s="3"/>
+      <c r="AC182" s="2"/>
+      <c r="AE182" s="4"/>
+    </row>
+    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A183" s="3"/>
+      <c r="AC183" s="2"/>
+      <c r="AE183" s="4"/>
+    </row>
+    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A184" s="3"/>
+      <c r="AC184" s="2"/>
+      <c r="AE184" s="4"/>
+    </row>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A185" s="3"/>
+      <c r="AC185" s="2"/>
+      <c r="AE185" s="4"/>
+    </row>
+    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A186" s="3"/>
+      <c r="AC186" s="2"/>
+      <c r="AE186" s="4"/>
+    </row>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A187" s="3"/>
+      <c r="AC187" s="2"/>
+      <c r="AE187" s="4"/>
+    </row>
+    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A188" s="3"/>
+      <c r="AC188" s="2"/>
+      <c r="AE188" s="4"/>
+    </row>
+    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A189" s="3"/>
+      <c r="AC189" s="2"/>
+      <c r="AE189" s="4"/>
+    </row>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="29:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="29:29" x14ac:dyDescent="0.25">
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC329" s="1"/>
-    </row>
   </sheetData>
+  <autoFilter ref="N1:AF1">
+    <sortState ref="N2:AE189">
+      <sortCondition ref="Z1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
